--- a/salidas/empresas/NOC.xlsx
+++ b/salidas/empresas/NOC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>36.20948791503906</v>
+        <v>36.20948028564453</v>
       </c>
       <c r="C2" t="n">
         <v>56.13445663452148</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>37.50565338134766</v>
+        <v>37.50563812255859</v>
       </c>
       <c r="C3" t="n">
         <v>57.91434860229492</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>39.95726013183594</v>
+        <v>39.95727157592773</v>
       </c>
       <c r="C4" t="n">
         <v>61.70001602172852</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>39.14396286010742</v>
+        <v>39.14397430419922</v>
       </c>
       <c r="C5" t="n">
         <v>60.44414901733398</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>38.01856231689453</v>
+        <v>38.01855087280273</v>
       </c>
       <c r="C6" t="n">
         <v>58.43838119506836</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>37.65412521362305</v>
+        <v>37.65412139892578</v>
       </c>
       <c r="C7" t="n">
         <v>57.87820816040039</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>38.90613174438477</v>
+        <v>38.9061279296875</v>
       </c>
       <c r="C8" t="n">
         <v>59.80266571044922</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>39.44995880126953</v>
+        <v>39.44995498657227</v>
       </c>
       <c r="C9" t="n">
         <v>60.36283493041992</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.19396591186523</v>
+        <v>40.19396209716797</v>
       </c>
       <c r="C10" t="n">
         <v>61.50124359130859</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>39.20196151733398</v>
+        <v>39.20194625854492</v>
       </c>
       <c r="C11" t="n">
         <v>59.98336410522461</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>39.69939422607422</v>
+        <v>39.69939804077148</v>
       </c>
       <c r="C12" t="n">
         <v>60.47125625610352</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.15613555908203</v>
+        <v>40.15612411499023</v>
       </c>
       <c r="C13" t="n">
         <v>61.16695022583008</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.07792282104492</v>
+        <v>42.07793426513672</v>
       </c>
       <c r="C14" t="n">
         <v>64.09429168701172</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>42.61769485473633</v>
+        <v>42.61769866943359</v>
       </c>
       <c r="C15" t="n">
         <v>64.91647338867188</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>44.25132369995117</v>
+        <v>44.2513542175293</v>
       </c>
       <c r="C16" t="n">
         <v>67.05776977539062</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>43.905517578125</v>
+        <v>43.90551376342773</v>
       </c>
       <c r="C17" t="n">
         <v>66.53373718261719</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>45.30167007446289</v>
+        <v>45.30167770385742</v>
       </c>
       <c r="C18" t="n">
         <v>68.31363677978516</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>45.59526824951172</v>
+        <v>45.59524917602539</v>
       </c>
       <c r="C20" t="n">
         <v>68.75634765625</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>46.95881271362305</v>
+        <v>46.95880889892578</v>
       </c>
       <c r="C22" t="n">
         <v>70.47299957275391</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>50.34226989746094</v>
+        <v>50.34224700927734</v>
       </c>
       <c r="C23" t="n">
         <v>75.55066680908203</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>47.56744384765625</v>
+        <v>47.56746292114258</v>
       </c>
       <c r="C25" t="n">
         <v>71.05123901367188</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>48.0029411315918</v>
+        <v>48.00296783447266</v>
       </c>
       <c r="C26" t="n">
         <v>71.70175933837891</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>47.76796340942383</v>
+        <v>47.76798629760742</v>
       </c>
       <c r="C27" t="n">
         <v>71.02413177490234</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>47.28183364868164</v>
+        <v>47.2818717956543</v>
       </c>
       <c r="C28" t="n">
         <v>70.30133819580078</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>44.70538711547852</v>
+        <v>44.70539093017578</v>
       </c>
       <c r="C29" t="n">
         <v>66.47049713134766</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>46.1005973815918</v>
+        <v>46.10056304931641</v>
       </c>
       <c r="C30" t="n">
         <v>68.17810821533203</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>40.87102890014648</v>
+        <v>40.87105560302734</v>
       </c>
       <c r="C31" t="n">
         <v>60.44414901733398</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>41.17039489746094</v>
+        <v>41.17038726806641</v>
       </c>
       <c r="C32" t="n">
         <v>60.88686370849609</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>42.30619812011719</v>
+        <v>42.30619430541992</v>
       </c>
       <c r="C33" t="n">
         <v>62.20597457885742</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.19994735717773</v>
+        <v>37.19995880126953</v>
       </c>
       <c r="C34" t="n">
         <v>54.69789123535156</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>28.81245040893555</v>
+        <v>28.81244850158691</v>
       </c>
       <c r="C35" t="n">
         <v>42.36511611938477</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>25.42019081115723</v>
+        <v>25.42018890380859</v>
       </c>
       <c r="C36" t="n">
         <v>36.99832534790039</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>27.95909881591797</v>
+        <v>27.95910835266113</v>
       </c>
       <c r="C37" t="n">
         <v>40.69364166259766</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>29.87104415893555</v>
+        <v>29.87104797363281</v>
       </c>
       <c r="C38" t="n">
         <v>43.47642135620117</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>23.42020988464355</v>
+        <v>23.42020034790039</v>
       </c>
       <c r="C39" t="n">
         <v>33.7547607421875</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>27.35699081420898</v>
+        <v>27.35700225830078</v>
       </c>
       <c r="C40" t="n">
         <v>39.42874145507812</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>30.30960273742676</v>
+        <v>30.30959701538086</v>
       </c>
       <c r="C41" t="n">
         <v>43.68422317504883</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>30.12187957763672</v>
+        <v>30.12187767028809</v>
       </c>
       <c r="C42" t="n">
         <v>43.0246696472168</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>28.89473724365234</v>
+        <v>28.89474678039551</v>
       </c>
       <c r="C43" t="n">
         <v>41.27188110351562</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>28.19892883300781</v>
+        <v>28.19894409179688</v>
       </c>
       <c r="C44" t="n">
         <v>40.27803039550781</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>31.14849662780762</v>
+        <v>31.14850234985352</v>
       </c>
       <c r="C45" t="n">
         <v>44.09983444213867</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>33.02469635009766</v>
+        <v>33.02469253540039</v>
       </c>
       <c r="C46" t="n">
         <v>46.75612640380859</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>31.99087142944336</v>
+        <v>31.99089050292969</v>
       </c>
       <c r="C47" t="n">
         <v>45.29245376586914</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>35.24192810058594</v>
+        <v>35.24193572998047</v>
       </c>
       <c r="C48" t="n">
         <v>49.51179885864258</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>35.91719055175781</v>
+        <v>35.91717910766602</v>
       </c>
       <c r="C49" t="n">
         <v>50.46047592163086</v>
@@ -1430,7 +1442,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>39.67289352416992</v>
+        <v>39.67288970947266</v>
       </c>
       <c r="C51" t="n">
         <v>55.34841156005859</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>42.464111328125</v>
+        <v>42.46412658691406</v>
       </c>
       <c r="C52" t="n">
         <v>59.24249649047852</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>43.92771148681641</v>
+        <v>43.92773056030273</v>
       </c>
       <c r="C53" t="n">
         <v>61.28440475463867</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>39.48258972167969</v>
+        <v>39.48257064819336</v>
       </c>
       <c r="C54" t="n">
         <v>54.65271377563477</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>35.53366851806641</v>
+        <v>35.53367614746094</v>
       </c>
       <c r="C55" t="n">
         <v>49.18653869628906</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>38.27507019042969</v>
+        <v>38.27506637573242</v>
       </c>
       <c r="C56" t="n">
         <v>52.98123931884766</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>35.62755966186523</v>
+        <v>35.62754821777344</v>
       </c>
       <c r="C57" t="n">
         <v>48.89741897583008</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>39.91313552856445</v>
+        <v>39.91313171386719</v>
       </c>
       <c r="C58" t="n">
         <v>54.77920532226562</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>41.61814117431641</v>
+        <v>41.61813735961914</v>
       </c>
       <c r="C59" t="n">
         <v>57.11927032470703</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>40.91811752319336</v>
+        <v>40.91812515258789</v>
       </c>
       <c r="C60" t="n">
         <v>55.72787857055664</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>42.97464370727539</v>
+        <v>42.97465133666992</v>
       </c>
       <c r="C61" t="n">
         <v>58.52872848510742</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>45.97319412231445</v>
+        <v>45.97316741943359</v>
       </c>
       <c r="C62" t="n">
         <v>62.612548828125</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>44.54796981811523</v>
+        <v>44.5479621887207</v>
       </c>
       <c r="C63" t="n">
         <v>60.24538040161133</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>46.37040328979492</v>
+        <v>46.37041473388672</v>
       </c>
       <c r="C64" t="n">
         <v>62.70999908447266</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>47.03590393066406</v>
+        <v>47.03591537475586</v>
       </c>
       <c r="C65" t="n">
         <v>63.61000061035156</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>48.65288543701172</v>
+        <v>48.65289306640625</v>
       </c>
       <c r="C66" t="n">
         <v>65.29000091552734</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>51.67832946777344</v>
+        <v>51.67831420898438</v>
       </c>
       <c r="C67" t="n">
         <v>69.34999847412109</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>45.09092330932617</v>
+        <v>45.09092712402344</v>
       </c>
       <c r="C68" t="n">
         <v>60.5099983215332</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>41.09151077270508</v>
+        <v>41.09151458740234</v>
       </c>
       <c r="C69" t="n">
         <v>54.61999893188477</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>39.24833679199219</v>
+        <v>39.24832153320312</v>
       </c>
       <c r="C70" t="n">
         <v>52.16999816894531</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>43.44626617431641</v>
+        <v>43.44626235961914</v>
       </c>
       <c r="C71" t="n">
         <v>57.75</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>43.33296585083008</v>
+        <v>43.33295822143555</v>
       </c>
       <c r="C72" t="n">
         <v>57.06999969482422</v>
@@ -2045,7 +2057,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>44.07708358764648</v>
+        <v>44.07707977294922</v>
       </c>
       <c r="C74" t="n">
         <v>58.04999923706055</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>45.79474258422852</v>
+        <v>45.79473495483398</v>
       </c>
       <c r="C75" t="n">
         <v>59.81000137329102</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>46.76716232299805</v>
+        <v>46.76715087890625</v>
       </c>
       <c r="C76" t="n">
         <v>61.08000183105469</v>
@@ -2161,7 +2173,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>45.40570831298828</v>
+        <v>45.40570068359375</v>
       </c>
       <c r="C78" t="n">
         <v>58.75</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>49.30092620849609</v>
+        <v>49.3009147644043</v>
       </c>
       <c r="C79" t="n">
         <v>63.79000091552734</v>
@@ -2248,7 +2260,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>52.1162109375</v>
+        <v>52.11621475219727</v>
       </c>
       <c r="C81" t="n">
         <v>66.88999938964844</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>51.7578239440918</v>
+        <v>51.75783538818359</v>
       </c>
       <c r="C82" t="n">
         <v>66.43000030517578</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>53.51866912841797</v>
+        <v>53.51866149902344</v>
       </c>
       <c r="C83" t="n">
         <v>68.69000244140625</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>52.41110992431641</v>
+        <v>52.4111213684082</v>
       </c>
       <c r="C84" t="n">
         <v>66.69999694824219</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>53.10261917114258</v>
+        <v>53.10261154174805</v>
       </c>
       <c r="C85" t="n">
         <v>67.58000183105469</v>
@@ -2422,7 +2434,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>52.04352951049805</v>
+        <v>52.04354095458984</v>
       </c>
       <c r="C87" t="n">
         <v>65.68000030517578</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>55.58547973632812</v>
+        <v>55.58548355102539</v>
       </c>
       <c r="C88" t="n">
         <v>70.15000152587891</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>60.01486206054688</v>
+        <v>60.01486968994141</v>
       </c>
       <c r="C89" t="n">
         <v>75.73999786376953</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>65.78042602539062</v>
+        <v>65.78045654296875</v>
       </c>
       <c r="C90" t="n">
         <v>82.38999938964844</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>66.10782623291016</v>
+        <v>66.10780334472656</v>
       </c>
       <c r="C91" t="n">
         <v>82.80000305175781</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>73.50099182128906</v>
+        <v>73.50100708007812</v>
       </c>
       <c r="C92" t="n">
         <v>92.05999755859375</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>74.15534210205078</v>
+        <v>74.15532684326172</v>
       </c>
       <c r="C93" t="n">
         <v>92.26999664306641</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>76.55832672119141</v>
+        <v>76.55838012695312</v>
       </c>
       <c r="C94" t="n">
         <v>95.26000213623047</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>86.40338134765625</v>
+        <v>86.40338897705078</v>
       </c>
       <c r="C95" t="n">
         <v>107.5100021362305</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>91.05442810058594</v>
+        <v>91.05446624755859</v>
       </c>
       <c r="C96" t="n">
         <v>112.6800003051758</v>
@@ -2741,7 +2753,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>93.37363433837891</v>
+        <v>93.37361907958984</v>
       </c>
       <c r="C98" t="n">
         <v>115.5500030517578</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>98.30703735351562</v>
+        <v>98.30702972412109</v>
       </c>
       <c r="C99" t="n">
         <v>121.0299987792969</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>100.2158279418945</v>
+        <v>100.2158203125</v>
       </c>
       <c r="C100" t="n">
         <v>123.379997253418</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>98.6968994140625</v>
+        <v>98.69691467285156</v>
       </c>
       <c r="C101" t="n">
         <v>121.5100021362305</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>99.307373046875</v>
+        <v>99.30738067626953</v>
       </c>
       <c r="C102" t="n">
         <v>121.5500030517578</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>97.73874664306641</v>
+        <v>97.73871612548828</v>
       </c>
       <c r="C103" t="n">
         <v>119.629997253418</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>100.7126235961914</v>
+        <v>100.7126541137695</v>
       </c>
       <c r="C104" t="n">
         <v>123.2699966430664</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>104.5131072998047</v>
+        <v>104.5130920410156</v>
       </c>
       <c r="C105" t="n">
         <v>127.2200012207031</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>108.2427749633789</v>
+        <v>108.2427520751953</v>
       </c>
       <c r="C106" t="n">
         <v>131.7599945068359</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>113.3361282348633</v>
+        <v>113.3361663818359</v>
       </c>
       <c r="C107" t="n">
         <v>137.9600067138672</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>116.3513870239258</v>
+        <v>116.3513717651367</v>
       </c>
       <c r="C108" t="n">
         <v>140.9299926757812</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>121.6847534179688</v>
+        <v>121.6847381591797</v>
       </c>
       <c r="C109" t="n">
         <v>147.3899993896484</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>129.5774688720703</v>
+        <v>129.5774536132812</v>
       </c>
       <c r="C110" t="n">
         <v>156.9499969482422</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>137.3798828125</v>
+        <v>137.3798980712891</v>
       </c>
       <c r="C111" t="n">
         <v>165.7100067138672</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>133.4420166015625</v>
+        <v>133.4419708251953</v>
       </c>
       <c r="C112" t="n">
         <v>160.9600067138672</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>127.7050399780273</v>
+        <v>127.7049789428711</v>
       </c>
       <c r="C113" t="n">
         <v>154.0399932861328</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>132.6322326660156</v>
+        <v>132.6322784423828</v>
       </c>
       <c r="C114" t="n">
         <v>159.1799926757812</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>132.1740264892578</v>
+        <v>132.1739959716797</v>
       </c>
       <c r="C115" t="n">
         <v>158.6300048828125</v>
@@ -3292,7 +3304,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>137.0986175537109</v>
+        <v>137.0986022949219</v>
       </c>
       <c r="C117" t="n">
         <v>163.7400054931641</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>138.9490051269531</v>
+        <v>138.9490203857422</v>
       </c>
       <c r="C118" t="n">
         <v>165.9499969482422</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>157.2020111083984</v>
+        <v>157.2020416259766</v>
       </c>
       <c r="C119" t="n">
         <v>187.75</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>156.7050170898438</v>
+        <v>156.7050628662109</v>
       </c>
       <c r="C120" t="n">
         <v>186.3600006103516</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>158.7651824951172</v>
+        <v>158.7651214599609</v>
       </c>
       <c r="C121" t="n">
         <v>188.8099975585938</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>155.6118774414062</v>
+        <v>155.6118927001953</v>
       </c>
       <c r="C122" t="n">
         <v>185.0599975585938</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>162.3158721923828</v>
+        <v>162.3159484863281</v>
       </c>
       <c r="C123" t="n">
         <v>192.2200012207031</v>
@@ -3524,7 +3536,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>179.5844116210938</v>
+        <v>179.5844421386719</v>
       </c>
       <c r="C126" t="n">
         <v>212.6699981689453</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>188.491455078125</v>
+        <v>188.4914398193359</v>
       </c>
       <c r="C127" t="n">
         <v>222.2799987792969</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>183.7003326416016</v>
+        <v>183.7003021240234</v>
       </c>
       <c r="C128" t="n">
         <v>216.6300048828125</v>
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>180.5930328369141</v>
+        <v>180.5929870605469</v>
       </c>
       <c r="C129" t="n">
         <v>212.0700073242188</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>182.1939697265625</v>
+        <v>182.1939239501953</v>
       </c>
       <c r="C130" t="n">
         <v>213.9499969482422</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>195.0101165771484</v>
+        <v>195.0101013183594</v>
       </c>
       <c r="C131" t="n">
         <v>229</v>
@@ -3756,7 +3768,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>198.7752838134766</v>
+        <v>198.7753295898438</v>
       </c>
       <c r="C133" t="n">
         <v>232.5800018310547</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>195.7840728759766</v>
+        <v>195.7840423583984</v>
       </c>
       <c r="C134" t="n">
         <v>229.0800018310547</v>
@@ -3843,7 +3855,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3872,7 +3884,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3901,7 +3913,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3930,7 +3942,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3959,7 +3971,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>226.5851745605469</v>
+        <v>226.5851287841797</v>
       </c>
       <c r="C140" t="n">
         <v>263.1300048828125</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>235.2730255126953</v>
+        <v>235.27294921875</v>
       </c>
       <c r="C141" t="n">
         <v>272.2099914550781</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>248.6784210205078</v>
+        <v>248.6783905029297</v>
       </c>
       <c r="C142" t="n">
         <v>287.7200012207031</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>255.4286193847656</v>
+        <v>255.4285583496094</v>
       </c>
       <c r="C143" t="n">
         <v>295.5299987792969</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>265.6879577636719</v>
+        <v>265.6879272460938</v>
       </c>
       <c r="C144" t="n">
         <v>307.3999938964844</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>266.1301879882812</v>
+        <v>266.1301574707031</v>
       </c>
       <c r="C145" t="n">
         <v>306.9100036621094</v>
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>295.2829284667969</v>
+        <v>295.2830200195312</v>
       </c>
       <c r="C146" t="n">
         <v>340.5299987792969</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>303.5293273925781</v>
+        <v>303.5293884277344</v>
       </c>
       <c r="C147" t="n">
         <v>350.0400085449219</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>303.7155151367188</v>
+        <v>303.715576171875</v>
       </c>
       <c r="C148" t="n">
         <v>349.1199951171875</v>
@@ -4249,7 +4261,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4278,7 +4290,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4307,7 +4319,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>262.3721618652344</v>
+        <v>262.3721313476562</v>
       </c>
       <c r="C152" t="n">
         <v>300.489990234375</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>261.6811218261719</v>
+        <v>261.6810913085938</v>
       </c>
       <c r="C153" t="n">
         <v>298.489990234375</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>278.2328796386719</v>
+        <v>278.2328491210938</v>
       </c>
       <c r="C154" t="n">
         <v>317.3699951171875</v>
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>229.6470947265625</v>
+        <v>229.6471405029297</v>
       </c>
       <c r="C155" t="n">
         <v>261.9500122070312</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>228.8860778808594</v>
+        <v>228.8861083984375</v>
       </c>
       <c r="C156" t="n">
         <v>259.8800048828125</v>
@@ -4481,7 +4493,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>242.6872100830078</v>
+        <v>242.6871643066406</v>
       </c>
       <c r="C158" t="n">
         <v>275.5499877929688</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>256.4490051269531</v>
+        <v>256.4490966796875</v>
       </c>
       <c r="C159" t="n">
         <v>289.9599914550781</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>238.4420776367188</v>
+        <v>238.4420623779297</v>
       </c>
       <c r="C160" t="n">
         <v>269.6000061035156</v>
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>256.40478515625</v>
+        <v>256.4048156738281</v>
       </c>
       <c r="C161" t="n">
         <v>289.9100036621094</v>
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>269.3507080078125</v>
+        <v>269.3507385253906</v>
       </c>
       <c r="C162" t="n">
         <v>303.25</v>
@@ -4655,7 +4667,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>306.9399108886719</v>
+        <v>306.93994140625</v>
       </c>
       <c r="C164" t="n">
         <v>345.5700073242188</v>
@@ -4713,7 +4725,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4742,7 +4754,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4771,11 +4783,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>314.2032165527344</v>
+        <v>314.2031860351562</v>
       </c>
       <c r="C167" t="n">
         <v>352.4800109863281</v>
@@ -4800,7 +4812,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>307.7684936523438</v>
+        <v>307.7685852050781</v>
       </c>
       <c r="C169" t="n">
         <v>343.9700012207031</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>335.1480102539062</v>
+        <v>335.1480407714844</v>
       </c>
       <c r="C170" t="n">
         <v>374.5700073242188</v>
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>295.3040466308594</v>
+        <v>295.3040771484375</v>
       </c>
       <c r="C171" t="n">
         <v>328.8399963378906</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>271.6951293945312</v>
+        <v>271.6950988769531</v>
       </c>
       <c r="C172" t="n">
         <v>302.5499877929688</v>
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>296.9473876953125</v>
+        <v>296.9474182128906</v>
       </c>
       <c r="C173" t="n">
         <v>330.6700134277344</v>
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>302.29443359375</v>
+        <v>302.2944030761719</v>
       </c>
       <c r="C174" t="n">
         <v>335.2000122070312</v>
@@ -5003,11 +5015,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>277.2594604492188</v>
+        <v>277.259521484375</v>
       </c>
       <c r="C175" t="n">
         <v>307.4400024414062</v>
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>293.1047058105469</v>
+        <v>293.1046447753906</v>
       </c>
       <c r="C176" t="n">
         <v>325.010009765625</v>
@@ -5061,7 +5073,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>285.7063598632812</v>
+        <v>285.7062683105469</v>
       </c>
       <c r="C178" t="n">
         <v>315.489990234375</v>
@@ -5119,11 +5131,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>262.4596862792969</v>
+        <v>262.4596252441406</v>
       </c>
       <c r="C179" t="n">
         <v>289.8200073242188</v>
@@ -5148,11 +5160,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>275.0023498535156</v>
+        <v>275.0022277832031</v>
       </c>
       <c r="C180" t="n">
         <v>302.260009765625</v>
@@ -5177,11 +5189,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>277.240478515625</v>
+        <v>277.2403869628906</v>
       </c>
       <c r="C181" t="n">
         <v>304.7200012207031</v>
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>260.7636413574219</v>
+        <v>260.7635192871094</v>
       </c>
       <c r="C182" t="n">
         <v>286.6099853515625</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>266.6388854980469</v>
+        <v>266.6389465332031</v>
       </c>
       <c r="C183" t="n">
         <v>291.6600036621094</v>
@@ -5264,7 +5276,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>324.0329895019531</v>
+        <v>324.0330810546875</v>
       </c>
       <c r="C185" t="n">
         <v>354.4400024414062</v>
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>335.9060363769531</v>
+        <v>335.9059448242188</v>
       </c>
       <c r="C186" t="n">
         <v>365.8699951171875</v>
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>333.6658935546875</v>
+        <v>333.665771484375</v>
       </c>
       <c r="C187" t="n">
         <v>363.4299926757812</v>
@@ -5380,7 +5392,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>339.0375061035156</v>
+        <v>339.0374755859375</v>
       </c>
       <c r="C189" t="n">
         <v>367.7000122070312</v>
@@ -5438,11 +5450,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>332.0760192871094</v>
+        <v>332.0759582519531</v>
       </c>
       <c r="C190" t="n">
         <v>360.1499938964844</v>
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>329.3743591308594</v>
+        <v>329.3743896484375</v>
       </c>
       <c r="C191" t="n">
         <v>357.2200012207031</v>
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>323.0140380859375</v>
+        <v>323.0141296386719</v>
       </c>
       <c r="C192" t="n">
         <v>348.7999877929688</v>
@@ -5525,11 +5537,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>358.4548645019531</v>
+        <v>358.4549255371094</v>
       </c>
       <c r="C193" t="n">
         <v>387.0700073242188</v>
@@ -5554,11 +5566,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>342.55419921875</v>
+        <v>342.5542297363281</v>
       </c>
       <c r="C194" t="n">
         <v>369.8999938964844</v>
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>411.0855712890625</v>
+        <v>411.0857238769531</v>
       </c>
       <c r="C195" t="n">
         <v>442.1400146484375</v>
@@ -5612,11 +5624,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>415.808837890625</v>
+        <v>415.8088684082031</v>
       </c>
       <c r="C196" t="n">
         <v>447.2200012207031</v>
@@ -5641,11 +5653,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>408.5381774902344</v>
+        <v>408.5381164550781</v>
       </c>
       <c r="C197" t="n">
         <v>439.3999938964844</v>
@@ -5670,11 +5682,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>436.7178039550781</v>
+        <v>436.7178344726562</v>
       </c>
       <c r="C198" t="n">
         <v>467.9700012207031</v>
@@ -5699,11 +5711,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>446.6099243164062</v>
+        <v>446.6098937988281</v>
       </c>
       <c r="C199" t="n">
         <v>478.5700073242188</v>
@@ -5728,7 +5740,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5757,11 +5769,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>447.634765625</v>
+        <v>447.6346740722656</v>
       </c>
       <c r="C201" t="n">
         <v>477.989990234375</v>
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>440.4518432617188</v>
+        <v>440.4518737792969</v>
       </c>
       <c r="C202" t="n">
         <v>470.3200073242188</v>
@@ -5815,7 +5827,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5844,11 +5856,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>501.0823364257812</v>
+        <v>501.0824584960938</v>
       </c>
       <c r="C204" t="n">
         <v>533.2899780273438</v>
@@ -5873,7 +5885,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5902,7 +5914,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>437.6703491210938</v>
+        <v>437.6703186035156</v>
       </c>
       <c r="C207" t="n">
         <v>464.1099853515625</v>
@@ -5960,11 +5972,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>435.41650390625</v>
+        <v>435.4164733886719</v>
       </c>
       <c r="C208" t="n">
         <v>461.7200012207031</v>
@@ -5989,7 +6001,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6018,7 +6030,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6047,11 +6059,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>431.6959228515625</v>
+        <v>431.6958923339844</v>
       </c>
       <c r="C211" t="n">
         <v>455.7999877929688</v>
@@ -6076,11 +6088,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>421.4670104980469</v>
+        <v>421.467041015625</v>
       </c>
       <c r="C212" t="n">
         <v>445</v>
@@ -6105,11 +6117,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>411.9694519042969</v>
+        <v>411.9693908691406</v>
       </c>
       <c r="C213" t="n">
         <v>433.0899963378906</v>
@@ -6134,11 +6146,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>418.72314453125</v>
+        <v>418.7232360839844</v>
       </c>
       <c r="C214" t="n">
         <v>440.1900024414062</v>
@@ -6163,7 +6175,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>453.7877807617188</v>
+        <v>453.7877197265625</v>
       </c>
       <c r="C216" t="n">
         <v>475.1600036621094</v>
@@ -6221,11 +6233,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>447.0835266113281</v>
+        <v>447.08349609375</v>
       </c>
       <c r="C217" t="n">
         <v>468.1400146484375</v>
@@ -6250,11 +6262,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>426.6651000976562</v>
+        <v>426.6651916503906</v>
       </c>
       <c r="C218" t="n">
         <v>446.760009765625</v>
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>442.0925598144531</v>
+        <v>442.092529296875</v>
       </c>
       <c r="C219" t="n">
         <v>461.0199890136719</v>
@@ -6308,11 +6320,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>459.0082397460938</v>
+        <v>459.00830078125</v>
       </c>
       <c r="C220" t="n">
         <v>478.6600036621094</v>
@@ -6337,7 +6349,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6366,11 +6378,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>434.1777648925781</v>
+        <v>434.1776733398438</v>
       </c>
       <c r="C222" t="n">
         <v>450.7699890136719</v>
@@ -6395,11 +6407,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>419.9032287597656</v>
+        <v>419.9031982421875</v>
       </c>
       <c r="C223" t="n">
         <v>435.9500122070312</v>
@@ -6424,11 +6436,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>466.4927673339844</v>
+        <v>466.4927978515625</v>
       </c>
       <c r="C224" t="n">
         <v>484.3200073242188</v>
@@ -6453,11 +6465,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>503.9512634277344</v>
+        <v>503.9512939453125</v>
       </c>
       <c r="C225" t="n">
         <v>523.2100219726562</v>
@@ -6482,11 +6494,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>510.6430053710938</v>
+        <v>510.6429443359375</v>
       </c>
       <c r="C226" t="n">
         <v>528.0700073242188</v>
@@ -6511,7 +6523,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6540,11 +6552,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>473.4908447265625</v>
+        <v>473.4907836914062</v>
       </c>
       <c r="C228" t="n">
         <v>489.6499938964844</v>
@@ -6569,11 +6581,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>455.719970703125</v>
+        <v>455.7200012207031</v>
       </c>
       <c r="C229" t="n">
         <v>469.2900085449219</v>
@@ -6598,7 +6610,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6627,7 +6639,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6656,7 +6668,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6685,7 +6697,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6714,11 +6726,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>472.8619689941406</v>
+        <v>472.8619995117188</v>
       </c>
       <c r="C234" t="n">
         <v>484.7699890136719</v>
@@ -6743,11 +6755,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>490.0334777832031</v>
+        <v>490.0334167480469</v>
       </c>
       <c r="C235" t="n">
         <v>499.9800109863281</v>
@@ -6772,7 +6784,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6801,11 +6813,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>578.3018188476562</v>
+        <v>578.3017578125</v>
       </c>
       <c r="C237" t="n">
         <v>590.0399780273438</v>
@@ -6830,11 +6842,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>599.5454711914062</v>
+        <v>599.5455322265625</v>
       </c>
       <c r="C238" t="n">
         <v>609.3200073242188</v>
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6888,11 +6900,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>563.0701904296875</v>
+        <v>563.0701293945312</v>
       </c>
       <c r="C240" t="n">
         <v>572.25</v>
@@ -6917,7 +6929,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>514.4199829101562</v>
+        <v>508.9800109863281</v>
       </c>
       <c r="C250" t="n">
-        <v>514.4199829101562</v>
+        <v>508.9800109863281</v>
       </c>
       <c r="D250" t="n">
-        <v>13957300</v>
+        <v>14494200</v>
       </c>
       <c r="E250" t="n">
         <v>31.43</v>
       </c>
       <c r="F250" t="n">
-        <v>16.36716458511474</v>
+        <v>16.19408243672695</v>
       </c>
       <c r="G250" t="n">
         <v>142063026</v>
       </c>
       <c r="H250" t="n">
-        <v>73080059407.08508</v>
+        <v>72307240534.23102</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09824723851792373</v>
+        <v>0.1020265470059747</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40107</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40107</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I7" t="n">
         <v>4.71627</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K7" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I8" t="n">
         <v>5.04153</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K8" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40388</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I9" t="n">
         <v>6.062485</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K9" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I10" t="n">
         <v>6.188975</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K10" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I11" t="n">
         <v>6.152835</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K11" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I12" t="n">
         <v>6.560479999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="K12" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I13" t="n">
         <v>6.25629</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="K13" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I14" t="n">
         <v>6.607445</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="K14" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40947</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I15" t="n">
         <v>7.550000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40947</v>
       </c>
       <c r="K15" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I16" t="n">
         <v>7.720000000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="K16" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I17" t="n">
         <v>7.789999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="K17" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I18" t="n">
         <v>7.75</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="K18" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41310</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I19" t="n">
         <v>7.800000000000001</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41310</v>
       </c>
       <c r="K19" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I20" t="n">
         <v>7.869999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="K20" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I21" t="n">
         <v>8.040000000000001</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K21" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I22" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="K22" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41673</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I23" t="n">
         <v>8.34</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41673</v>
       </c>
       <c r="K23" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I24" t="n">
         <v>8.940000000000001</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="K24" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I25" t="n">
         <v>9.26</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="K25" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I26" t="n">
         <v>9.379999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="K26" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42037</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I27" t="n">
         <v>9.74</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42037</v>
       </c>
       <c r="K27" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I28" t="n">
         <v>9.52</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K28" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I29" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K29" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I30" t="n">
         <v>10.38</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="K30" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I31" t="n">
         <v>10.39</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="K31" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I32" t="n">
         <v>11.01</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="K32" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I33" t="n">
         <v>11.12</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K33" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I34" t="n">
         <v>11.72</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="K34" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42765</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I35" t="n">
         <v>12.19</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42765</v>
       </c>
       <c r="K35" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I36" t="n">
         <v>12.79</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="K36" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I37" t="n">
         <v>13.09</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="K37" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I38" t="n">
         <v>13.42</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="K38" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43129</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I39" t="n">
         <v>11.47</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43129</v>
       </c>
       <c r="K39" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I40" t="n">
         <v>12.05</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="K40" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I41" t="n">
         <v>12.83</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K41" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I42" t="n">
         <v>15.69</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="K42" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I43" t="n">
         <v>16.74</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="K43" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I44" t="n">
         <v>17.59</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="K44" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I45" t="n">
         <v>18.72</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="K45" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I46" t="n">
         <v>17.67</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="K46" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43860</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I47" t="n">
         <v>13.18</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43860</v>
       </c>
       <c r="K47" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I48" t="n">
         <v>13.27</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K48" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I49" t="n">
         <v>14.22</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K49" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I50" t="n">
         <v>14.62</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="K50" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I51" t="n">
         <v>19.02</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="K51" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I52" t="n">
         <v>27.3</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I53" t="n">
         <v>27.71</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I54" t="n">
         <v>28.45</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K54" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44588</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I55" t="n">
         <v>43.53999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44588</v>
       </c>
       <c r="K55" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I56" t="n">
         <v>36.20999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I57" t="n">
         <v>35.84999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K57" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I58" t="n">
         <v>35.11</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K58" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44952</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I59" t="n">
         <v>31.47</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44952</v>
       </c>
       <c r="K59" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I60" t="n">
         <v>30.87</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I61" t="n">
         <v>30.15</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I62" t="n">
         <v>30.44</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K62" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45316</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I63" t="n">
         <v>13.53</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45316</v>
       </c>
       <c r="K63" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I64" t="n">
         <v>14.35</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K64" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I65" t="n">
         <v>15.37</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K65" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I66" t="n">
         <v>16.19</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="K66" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I67" t="n">
         <v>28.34</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="K67" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I68" t="n">
         <v>25.34</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="K68" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I69" t="n">
         <v>27.13</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="K69" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I70" t="n">
         <v>27.8</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="K70" t="n">
@@ -10451,13 +10463,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46049</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10484,7 +10496,7 @@
       <c r="I71" t="n">
         <v>29.08</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46049</v>
       </c>
       <c r="K71" t="n">
@@ -10497,13 +10509,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10530,7 +10542,7 @@
       <c r="I72" t="n">
         <v>31.9</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="K72" t="n">
@@ -10543,13 +10555,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10576,7 +10588,7 @@
       <c r="I73" t="n">
         <v>31.43</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="K73" t="n">
@@ -10613,52 +10625,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40015</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="C2" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40105</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40107</v>
       </c>
       <c r="C3" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40214</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40218</v>
       </c>
       <c r="C4" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40294</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="C5" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40386</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40388</v>
       </c>
       <c r="C6" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40476</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="C7" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40581</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="C8" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40658</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="C9" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40749</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="C10" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40840</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="C11" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40945</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40947</v>
       </c>
       <c r="C12" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41019</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="C13" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41110</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="C14" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41201</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="C15" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41310</v>
       </c>
       <c r="C16" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41383</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="C17" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41474</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C18" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41565</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="C19" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41669</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41673</v>
       </c>
       <c r="C20" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41746</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="C21" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41838</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="C22" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41929</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="C23" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42033</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42037</v>
       </c>
       <c r="C24" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C25" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42209</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C26" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="C27" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42397</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="C28" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42482</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="C29" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42573</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C30" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="C31" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42761</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42765</v>
       </c>
       <c r="C32" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="C33" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42937</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="C34" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="C35" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43125</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43129</v>
       </c>
       <c r="C36" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="C37" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43301</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C38" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="C39" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43493</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="C40" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43574</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="C41" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43665</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="C42" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43759</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="C43" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43857</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43860</v>
       </c>
       <c r="C44" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43945</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C45" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C46" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44123</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="C47" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44221</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="C48" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44312</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C49" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44403</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C50" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44494</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C51" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44585</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44588</v>
       </c>
       <c r="C52" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44676</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C53" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44767</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C54" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44858</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C55" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44949</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44952</v>
       </c>
       <c r="C56" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45040</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C57" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C58" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C59" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45313</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45316</v>
       </c>
       <c r="C60" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45404</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C61" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45495</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C62" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45586</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="C63" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45684</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="C64" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45764</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="C65" t="n">
@@ -12703,10 +12715,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="C66" t="n">
@@ -12735,10 +12747,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45946</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="C67" t="n">
@@ -12767,10 +12779,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46044</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46049</v>
       </c>
       <c r="C68" t="n">
@@ -12799,10 +12811,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46128</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C69" t="n">
@@ -12831,10 +12843,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="C70" t="n">
@@ -12881,12 +12893,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/NOC.xlsx
+++ b/salidas/empresas/NOC.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>36.20948028564453</v>
+        <v>36.20948791503906</v>
       </c>
       <c r="C2" t="n">
         <v>56.13445663452148</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>37.50563812255859</v>
+        <v>37.50564575195312</v>
       </c>
       <c r="C3" t="n">
         <v>57.91434860229492</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>39.95727157592773</v>
+        <v>39.95725631713867</v>
       </c>
       <c r="C4" t="n">
         <v>61.70001602172852</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>39.14397430419922</v>
+        <v>39.14394760131836</v>
       </c>
       <c r="C5" t="n">
         <v>60.44414901733398</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>38.01855087280273</v>
+        <v>38.01856231689453</v>
       </c>
       <c r="C6" t="n">
         <v>58.43838119506836</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>37.65412139892578</v>
+        <v>37.65411758422852</v>
       </c>
       <c r="C7" t="n">
         <v>57.87820816040039</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>38.9061279296875</v>
+        <v>38.90613174438477</v>
       </c>
       <c r="C8" t="n">
         <v>59.80266571044922</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>39.44995498657227</v>
+        <v>39.44997024536133</v>
       </c>
       <c r="C9" t="n">
         <v>60.36283493041992</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.19396209716797</v>
+        <v>40.1939582824707</v>
       </c>
       <c r="C10" t="n">
         <v>61.50124359130859</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>39.20194625854492</v>
+        <v>39.20196533203125</v>
       </c>
       <c r="C11" t="n">
         <v>59.98336410522461</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>39.69939804077148</v>
+        <v>39.69939041137695</v>
       </c>
       <c r="C12" t="n">
         <v>60.47125625610352</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.15612411499023</v>
+        <v>40.15613555908203</v>
       </c>
       <c r="C13" t="n">
         <v>61.16695022583008</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.07793426513672</v>
+        <v>42.07792663574219</v>
       </c>
       <c r="C14" t="n">
         <v>64.09429168701172</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>42.61769866943359</v>
+        <v>42.61769485473633</v>
       </c>
       <c r="C15" t="n">
         <v>64.91647338867188</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>44.2513542175293</v>
+        <v>44.2513427734375</v>
       </c>
       <c r="C16" t="n">
         <v>67.05776977539062</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>43.90551376342773</v>
+        <v>43.90552139282227</v>
       </c>
       <c r="C17" t="n">
         <v>66.53373718261719</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>46.6557502746582</v>
+        <v>46.65573883056641</v>
       </c>
       <c r="C19" t="n">
         <v>70.35554504394531</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>45.59524917602539</v>
+        <v>45.59526443481445</v>
       </c>
       <c r="C20" t="n">
         <v>68.75634765625</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>47.46453857421875</v>
+        <v>47.46451950073242</v>
       </c>
       <c r="C21" t="n">
         <v>71.23194122314453</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>46.95880889892578</v>
+        <v>46.95880126953125</v>
       </c>
       <c r="C22" t="n">
         <v>70.47299957275391</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>47.65816497802734</v>
+        <v>47.65818405151367</v>
       </c>
       <c r="C24" t="n">
         <v>71.186767578125</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>47.56746292114258</v>
+        <v>47.56744003295898</v>
       </c>
       <c r="C25" t="n">
         <v>71.05123901367188</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>48.00296783447266</v>
+        <v>48.00295257568359</v>
       </c>
       <c r="C26" t="n">
         <v>71.70175933837891</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>47.76798629760742</v>
+        <v>47.76797103881836</v>
       </c>
       <c r="C27" t="n">
         <v>71.02413177490234</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>47.2818717956543</v>
+        <v>47.28185272216797</v>
       </c>
       <c r="C28" t="n">
         <v>70.30133819580078</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>44.70539093017578</v>
+        <v>44.70537948608398</v>
       </c>
       <c r="C29" t="n">
         <v>66.47049713134766</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>46.10056304931641</v>
+        <v>46.10057830810547</v>
       </c>
       <c r="C30" t="n">
         <v>68.17810821533203</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>40.87105560302734</v>
+        <v>40.87104034423828</v>
       </c>
       <c r="C31" t="n">
         <v>60.44414901733398</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>41.17038726806641</v>
+        <v>41.17038345336914</v>
       </c>
       <c r="C32" t="n">
         <v>60.88686370849609</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>42.30619430541992</v>
+        <v>42.30618667602539</v>
       </c>
       <c r="C33" t="n">
         <v>62.20597457885742</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.19995880126953</v>
+        <v>37.19994735717773</v>
       </c>
       <c r="C34" t="n">
         <v>54.69789123535156</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>28.81244850158691</v>
+        <v>28.81245803833008</v>
       </c>
       <c r="C35" t="n">
         <v>42.36511611938477</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>25.42018890380859</v>
+        <v>25.42019462585449</v>
       </c>
       <c r="C36" t="n">
         <v>36.99832534790039</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>27.95910835266113</v>
+        <v>27.95909881591797</v>
       </c>
       <c r="C37" t="n">
         <v>40.69364166259766</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>29.87104797363281</v>
+        <v>29.87104606628418</v>
       </c>
       <c r="C38" t="n">
         <v>43.47642135620117</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>27.35700225830078</v>
+        <v>27.35700035095215</v>
       </c>
       <c r="C40" t="n">
         <v>39.42874145507812</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>30.30959701538086</v>
+        <v>30.30960083007812</v>
       </c>
       <c r="C41" t="n">
         <v>43.68422317504883</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>30.12187767028809</v>
+        <v>30.12186431884766</v>
       </c>
       <c r="C42" t="n">
         <v>43.0246696472168</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>28.89474678039551</v>
+        <v>28.89472579956055</v>
       </c>
       <c r="C43" t="n">
         <v>41.27188110351562</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>28.19894409179688</v>
+        <v>28.19893836975098</v>
       </c>
       <c r="C44" t="n">
         <v>40.27803039550781</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>31.14850234985352</v>
+        <v>31.14851379394531</v>
       </c>
       <c r="C45" t="n">
         <v>44.09983444213867</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>33.02469253540039</v>
+        <v>33.02470016479492</v>
       </c>
       <c r="C46" t="n">
         <v>46.75612640380859</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>31.99089050292969</v>
+        <v>31.99086952209473</v>
       </c>
       <c r="C47" t="n">
         <v>45.29245376586914</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>35.24193572998047</v>
+        <v>35.24192428588867</v>
       </c>
       <c r="C48" t="n">
         <v>49.51179885864258</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>36.39951705932617</v>
+        <v>36.39950180053711</v>
       </c>
       <c r="C50" t="n">
         <v>51.13809967041016</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>42.46412658691406</v>
+        <v>42.46411514282227</v>
       </c>
       <c r="C52" t="n">
         <v>59.24249649047852</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>43.92773056030273</v>
+        <v>43.92772674560547</v>
       </c>
       <c r="C53" t="n">
         <v>61.28440475463867</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>39.48257064819336</v>
+        <v>39.48258209228516</v>
       </c>
       <c r="C54" t="n">
         <v>54.65271377563477</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>35.53367614746094</v>
+        <v>35.5336799621582</v>
       </c>
       <c r="C55" t="n">
         <v>49.18653869628906</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>38.27506637573242</v>
+        <v>38.27503967285156</v>
       </c>
       <c r="C56" t="n">
         <v>52.98123931884766</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>35.62754821777344</v>
+        <v>35.62754440307617</v>
       </c>
       <c r="C57" t="n">
         <v>48.89741897583008</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>39.91313171386719</v>
+        <v>39.91312026977539</v>
       </c>
       <c r="C58" t="n">
         <v>54.77920532226562</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>41.61813735961914</v>
+        <v>41.61814498901367</v>
       </c>
       <c r="C59" t="n">
         <v>57.11927032470703</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>40.91812515258789</v>
+        <v>40.91811752319336</v>
       </c>
       <c r="C60" t="n">
         <v>55.72787857055664</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>45.97316741943359</v>
+        <v>45.97319030761719</v>
       </c>
       <c r="C62" t="n">
         <v>62.612548828125</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>44.5479621887207</v>
+        <v>44.54798126220703</v>
       </c>
       <c r="C63" t="n">
         <v>60.24538040161133</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>47.03591537475586</v>
+        <v>47.03590393066406</v>
       </c>
       <c r="C65" t="n">
         <v>63.61000061035156</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>48.65289306640625</v>
+        <v>48.65288925170898</v>
       </c>
       <c r="C66" t="n">
         <v>65.29000091552734</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>51.67831420898438</v>
+        <v>51.6783332824707</v>
       </c>
       <c r="C67" t="n">
         <v>69.34999847412109</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>45.09092712402344</v>
+        <v>45.09091949462891</v>
       </c>
       <c r="C68" t="n">
         <v>60.5099983215332</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>39.24832153320312</v>
+        <v>39.24833297729492</v>
       </c>
       <c r="C70" t="n">
         <v>52.16999816894531</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>43.44626235961914</v>
+        <v>43.44625091552734</v>
       </c>
       <c r="C71" t="n">
         <v>57.75</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>43.33295822143555</v>
+        <v>43.33297348022461</v>
       </c>
       <c r="C72" t="n">
         <v>57.06999969482422</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>44.4035758972168</v>
+        <v>44.40359115600586</v>
       </c>
       <c r="C73" t="n">
         <v>58.47999954223633</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>44.07707977294922</v>
+        <v>44.07708358764648</v>
       </c>
       <c r="C74" t="n">
         <v>58.04999923706055</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>45.79473495483398</v>
+        <v>45.79473876953125</v>
       </c>
       <c r="C75" t="n">
         <v>59.81000137329102</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>46.76715087890625</v>
+        <v>46.76713943481445</v>
       </c>
       <c r="C76" t="n">
         <v>61.08000183105469</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>48.45162582397461</v>
+        <v>48.45162200927734</v>
       </c>
       <c r="C77" t="n">
         <v>63.27999877929688</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>45.40570068359375</v>
+        <v>45.40568923950195</v>
       </c>
       <c r="C78" t="n">
         <v>58.75</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>49.3009147644043</v>
+        <v>49.30090713500977</v>
       </c>
       <c r="C79" t="n">
         <v>63.79000091552734</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>51.16352081298828</v>
+        <v>51.16353225708008</v>
       </c>
       <c r="C80" t="n">
         <v>66.19999694824219</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>52.11621475219727</v>
+        <v>52.1162109375</v>
       </c>
       <c r="C81" t="n">
         <v>66.88999938964844</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>51.75783538818359</v>
+        <v>51.75782775878906</v>
       </c>
       <c r="C82" t="n">
         <v>66.43000030517578</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>53.51866149902344</v>
+        <v>53.51868057250977</v>
       </c>
       <c r="C83" t="n">
         <v>68.69000244140625</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>52.4111213684082</v>
+        <v>52.41111755371094</v>
       </c>
       <c r="C84" t="n">
         <v>66.69999694824219</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>53.10261154174805</v>
+        <v>53.10260772705078</v>
       </c>
       <c r="C85" t="n">
         <v>67.58000183105469</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>51.10674285888672</v>
+        <v>51.10675048828125</v>
       </c>
       <c r="C86" t="n">
         <v>65.04000091552734</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>55.58548355102539</v>
+        <v>55.58546447753906</v>
       </c>
       <c r="C88" t="n">
         <v>70.15000152587891</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>60.01486968994141</v>
+        <v>60.01485824584961</v>
       </c>
       <c r="C89" t="n">
         <v>75.73999786376953</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>73.50100708007812</v>
+        <v>73.50099182128906</v>
       </c>
       <c r="C92" t="n">
         <v>92.05999755859375</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>76.55838012695312</v>
+        <v>76.55831146240234</v>
       </c>
       <c r="C94" t="n">
         <v>95.26000213623047</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>91.05446624755859</v>
+        <v>91.05443572998047</v>
       </c>
       <c r="C96" t="n">
         <v>112.6800003051758</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>92.61404418945312</v>
+        <v>92.61402893066406</v>
       </c>
       <c r="C97" t="n">
         <v>114.6100006103516</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>93.37361907958984</v>
+        <v>93.37364196777344</v>
       </c>
       <c r="C98" t="n">
         <v>115.5500030517578</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>98.30702972412109</v>
+        <v>98.30703735351562</v>
       </c>
       <c r="C99" t="n">
         <v>121.0299987792969</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>100.2158203125</v>
+        <v>100.2157897949219</v>
       </c>
       <c r="C100" t="n">
         <v>123.379997253418</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>98.69691467285156</v>
+        <v>98.6968994140625</v>
       </c>
       <c r="C101" t="n">
         <v>121.5100021362305</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>99.30738067626953</v>
+        <v>99.30740356445312</v>
       </c>
       <c r="C102" t="n">
         <v>121.5500030517578</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>97.73871612548828</v>
+        <v>97.73874664306641</v>
       </c>
       <c r="C103" t="n">
         <v>119.629997253418</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>100.7126541137695</v>
+        <v>100.712646484375</v>
       </c>
       <c r="C104" t="n">
         <v>123.2699966430664</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>104.5130920410156</v>
+        <v>104.5130767822266</v>
       </c>
       <c r="C105" t="n">
         <v>127.2200012207031</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>108.2427520751953</v>
+        <v>108.2427444458008</v>
       </c>
       <c r="C106" t="n">
         <v>131.7599945068359</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>113.3361663818359</v>
+        <v>113.3361282348633</v>
       </c>
       <c r="C107" t="n">
         <v>137.9600067138672</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>121.6847381591797</v>
+        <v>121.6847610473633</v>
       </c>
       <c r="C109" t="n">
         <v>147.3899993896484</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>137.3798980712891</v>
+        <v>137.3799438476562</v>
       </c>
       <c r="C111" t="n">
         <v>165.7100067138672</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>133.4419708251953</v>
+        <v>133.4419555664062</v>
       </c>
       <c r="C112" t="n">
         <v>160.9600067138672</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>127.7049789428711</v>
+        <v>127.7050399780273</v>
       </c>
       <c r="C113" t="n">
         <v>154.0399932861328</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>132.6322784423828</v>
+        <v>132.6323089599609</v>
       </c>
       <c r="C114" t="n">
         <v>159.1799926757812</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>132.1739959716797</v>
+        <v>132.1740112304688</v>
       </c>
       <c r="C115" t="n">
         <v>158.6300048828125</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>144.1557464599609</v>
+        <v>144.1557006835938</v>
       </c>
       <c r="C116" t="n">
         <v>173.0099945068359</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>137.0986022949219</v>
+        <v>137.0986328125</v>
       </c>
       <c r="C117" t="n">
         <v>163.7400054931641</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>138.9490203857422</v>
+        <v>138.9489898681641</v>
       </c>
       <c r="C118" t="n">
         <v>165.9499969482422</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>157.2020416259766</v>
+        <v>157.2020263671875</v>
       </c>
       <c r="C119" t="n">
         <v>187.75</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>156.7050628662109</v>
+        <v>156.7050170898438</v>
       </c>
       <c r="C120" t="n">
         <v>186.3600006103516</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>158.7651214599609</v>
+        <v>158.7651519775391</v>
       </c>
       <c r="C121" t="n">
         <v>188.8099975585938</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>155.6118927001953</v>
+        <v>155.6118774414062</v>
       </c>
       <c r="C122" t="n">
         <v>185.0599975585938</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>162.3159484863281</v>
+        <v>162.3159332275391</v>
       </c>
       <c r="C123" t="n">
         <v>192.2200012207031</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>167.1122436523438</v>
+        <v>167.1122283935547</v>
       </c>
       <c r="C124" t="n">
         <v>197.8999938964844</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>174.1716766357422</v>
+        <v>174.1717071533203</v>
       </c>
       <c r="C125" t="n">
         <v>206.2599945068359</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>179.5844421386719</v>
+        <v>179.5844573974609</v>
       </c>
       <c r="C126" t="n">
         <v>212.6699981689453</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>188.4914398193359</v>
+        <v>188.4914855957031</v>
       </c>
       <c r="C127" t="n">
         <v>222.2799987792969</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>183.7003021240234</v>
+        <v>183.7003326416016</v>
       </c>
       <c r="C128" t="n">
         <v>216.6300048828125</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>180.5929870605469</v>
+        <v>180.5929718017578</v>
       </c>
       <c r="C129" t="n">
         <v>212.0700073242188</v>
@@ -3714,7 +3714,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>182.1939239501953</v>
+        <v>182.1939086914062</v>
       </c>
       <c r="C130" t="n">
         <v>213.9499969482422</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>195.0101013183594</v>
+        <v>195.0100860595703</v>
       </c>
       <c r="C131" t="n">
         <v>229</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>198.7753295898438</v>
+        <v>198.7753143310547</v>
       </c>
       <c r="C133" t="n">
         <v>232.5800018310547</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>211.1763916015625</v>
+        <v>211.1763610839844</v>
       </c>
       <c r="C135" t="n">
         <v>247.0899963378906</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>204.0174407958984</v>
+        <v>204.0174713134766</v>
       </c>
       <c r="C136" t="n">
         <v>237.8399963378906</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>210.9827575683594</v>
+        <v>210.9826965332031</v>
       </c>
       <c r="C137" t="n">
         <v>245.9600067138672</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>222.3570404052734</v>
+        <v>222.3570556640625</v>
       </c>
       <c r="C138" t="n">
         <v>259.2200012207031</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>226.5851287841797</v>
+        <v>226.5850830078125</v>
       </c>
       <c r="C140" t="n">
         <v>263.1300048828125</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>235.27294921875</v>
+        <v>235.2729797363281</v>
       </c>
       <c r="C141" t="n">
         <v>272.2099914550781</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>248.6783905029297</v>
+        <v>248.6783447265625</v>
       </c>
       <c r="C142" t="n">
         <v>287.7200012207031</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>265.6879272460938</v>
+        <v>265.6878967285156</v>
       </c>
       <c r="C144" t="n">
         <v>307.3999938964844</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>295.2830200195312</v>
+        <v>295.2829284667969</v>
       </c>
       <c r="C146" t="n">
         <v>340.5299987792969</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>303.5293884277344</v>
+        <v>303.529296875</v>
       </c>
       <c r="C147" t="n">
         <v>350.0400085449219</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>303.715576171875</v>
+        <v>303.7155151367188</v>
       </c>
       <c r="C148" t="n">
         <v>349.1199951171875</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>280.1574096679688</v>
+        <v>280.1574401855469</v>
       </c>
       <c r="C149" t="n">
         <v>322.0400085449219</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>284.6898498535156</v>
+        <v>284.6898193359375</v>
       </c>
       <c r="C150" t="n">
         <v>327.25</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>268.6676025390625</v>
+        <v>268.6675720214844</v>
       </c>
       <c r="C151" t="n">
         <v>307.7000122070312</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>261.6810913085938</v>
+        <v>261.6811828613281</v>
       </c>
       <c r="C153" t="n">
         <v>298.489990234375</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>278.2328491210938</v>
+        <v>278.2327880859375</v>
       </c>
       <c r="C154" t="n">
         <v>317.3699951171875</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>229.6471405029297</v>
+        <v>229.6471557617188</v>
       </c>
       <c r="C155" t="n">
         <v>261.9500122070312</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>228.8861083984375</v>
+        <v>228.8860931396484</v>
       </c>
       <c r="C156" t="n">
         <v>259.8800048828125</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>215.6926116943359</v>
+        <v>215.692626953125</v>
       </c>
       <c r="C157" t="n">
         <v>244.8999938964844</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>256.4490966796875</v>
+        <v>256.4490661621094</v>
       </c>
       <c r="C159" t="n">
         <v>289.9599914550781</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>238.4420623779297</v>
+        <v>238.4419860839844</v>
       </c>
       <c r="C160" t="n">
         <v>269.6000061035156</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>256.4048156738281</v>
+        <v>256.40478515625</v>
       </c>
       <c r="C161" t="n">
         <v>289.9100036621094</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>286.9906616210938</v>
+        <v>286.9905700683594</v>
       </c>
       <c r="C163" t="n">
         <v>323.1099853515625</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>326.7471008300781</v>
+        <v>326.7470092773438</v>
       </c>
       <c r="C165" t="n">
         <v>367.8699951171875</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>334.0905151367188</v>
+        <v>334.0904235839844</v>
       </c>
       <c r="C166" t="n">
         <v>374.7900085449219</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>314.7476196289062</v>
+        <v>314.7475891113281</v>
       </c>
       <c r="C168" t="n">
         <v>351.7699890136719</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>307.7685852050781</v>
+        <v>307.7685546875</v>
       </c>
       <c r="C169" t="n">
         <v>343.9700012207031</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>335.1480407714844</v>
+        <v>335.1480102539062</v>
       </c>
       <c r="C170" t="n">
         <v>374.5700073242188</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>295.3040771484375</v>
+        <v>295.303955078125</v>
       </c>
       <c r="C171" t="n">
         <v>328.8399963378906</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>271.6950988769531</v>
+        <v>271.6951599121094</v>
       </c>
       <c r="C172" t="n">
         <v>302.5499877929688</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>296.9474182128906</v>
+        <v>296.9474487304688</v>
       </c>
       <c r="C173" t="n">
         <v>330.6700134277344</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>302.2944030761719</v>
+        <v>302.2943725585938</v>
       </c>
       <c r="C174" t="n">
         <v>335.2000122070312</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>277.259521484375</v>
+        <v>277.2594604492188</v>
       </c>
       <c r="C175" t="n">
         <v>307.4400024414062</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>293.1046447753906</v>
+        <v>293.1047058105469</v>
       </c>
       <c r="C176" t="n">
         <v>325.010009765625</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>310.2660217285156</v>
+        <v>310.2660522460938</v>
       </c>
       <c r="C177" t="n">
         <v>342.6099853515625</v>
@@ -5106,7 +5106,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>285.7062683105469</v>
+        <v>285.7062377929688</v>
       </c>
       <c r="C178" t="n">
         <v>315.489990234375</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>262.4596252441406</v>
+        <v>262.4596862792969</v>
       </c>
       <c r="C179" t="n">
         <v>289.8200073242188</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>275.0022277832031</v>
+        <v>275.0022583007812</v>
       </c>
       <c r="C180" t="n">
         <v>302.260009765625</v>
@@ -5193,7 +5193,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>277.2403869628906</v>
+        <v>277.2403564453125</v>
       </c>
       <c r="C181" t="n">
         <v>304.7200012207031</v>
@@ -5251,7 +5251,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>266.6389465332031</v>
+        <v>266.6388549804688</v>
       </c>
       <c r="C183" t="n">
         <v>291.6600036621094</v>
@@ -5280,7 +5280,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>295.8753967285156</v>
+        <v>295.8753662109375</v>
       </c>
       <c r="C184" t="n">
         <v>323.6400146484375</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>324.0330810546875</v>
+        <v>324.0330505371094</v>
       </c>
       <c r="C185" t="n">
         <v>354.4400024414062</v>
@@ -5338,7 +5338,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>335.9059448242188</v>
+        <v>335.9059753417969</v>
       </c>
       <c r="C186" t="n">
         <v>365.8699951171875</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>333.665771484375</v>
+        <v>333.6658630371094</v>
       </c>
       <c r="C187" t="n">
         <v>363.4299926757812</v>
@@ -5396,7 +5396,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>333.2894287109375</v>
+        <v>333.2893981933594</v>
       </c>
       <c r="C188" t="n">
         <v>363.0199890136719</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>332.0759582519531</v>
+        <v>332.0760192871094</v>
       </c>
       <c r="C190" t="n">
         <v>360.1499938964844</v>
@@ -5512,7 +5512,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>323.0141296386719</v>
+        <v>323.0140991210938</v>
       </c>
       <c r="C192" t="n">
         <v>348.7999877929688</v>
@@ -5541,7 +5541,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>358.4549255371094</v>
+        <v>358.4549560546875</v>
       </c>
       <c r="C193" t="n">
         <v>387.0700073242188</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>342.5542297363281</v>
+        <v>342.5542602539062</v>
       </c>
       <c r="C194" t="n">
         <v>369.8999938964844</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>411.0857238769531</v>
+        <v>411.0856323242188</v>
       </c>
       <c r="C195" t="n">
         <v>442.1400146484375</v>
@@ -5628,7 +5628,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>415.8088684082031</v>
+        <v>415.8088989257812</v>
       </c>
       <c r="C196" t="n">
         <v>447.2200012207031</v>
@@ -5657,7 +5657,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>408.5381164550781</v>
+        <v>408.5380554199219</v>
       </c>
       <c r="C197" t="n">
         <v>439.3999938964844</v>
@@ -5686,7 +5686,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>436.7178344726562</v>
+        <v>436.7178039550781</v>
       </c>
       <c r="C198" t="n">
         <v>467.9700012207031</v>
@@ -5744,7 +5744,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>446.9178466796875</v>
+        <v>446.9178771972656</v>
       </c>
       <c r="C200" t="n">
         <v>478.8999938964844</v>
@@ -5773,7 +5773,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>447.6346740722656</v>
+        <v>447.634765625</v>
       </c>
       <c r="C201" t="n">
         <v>477.989990234375</v>
@@ -5802,7 +5802,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>440.4518737792969</v>
+        <v>440.4518127441406</v>
       </c>
       <c r="C202" t="n">
         <v>470.3200073242188</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>514.14453125</v>
+        <v>514.1444702148438</v>
       </c>
       <c r="C203" t="n">
         <v>549.010009765625</v>
@@ -5889,7 +5889,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>512.6583862304688</v>
+        <v>512.6582641601562</v>
       </c>
       <c r="C205" t="n">
         <v>545.6099853515625</v>
@@ -5918,7 +5918,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>420.9809875488281</v>
+        <v>420.9810485839844</v>
       </c>
       <c r="C206" t="n">
         <v>448.0400085449219</v>
@@ -5947,7 +5947,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>437.6703186035156</v>
+        <v>437.6702880859375</v>
       </c>
       <c r="C207" t="n">
         <v>464.1099853515625</v>
@@ -5976,7 +5976,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>435.4164733886719</v>
+        <v>435.41650390625</v>
       </c>
       <c r="C208" t="n">
         <v>461.7200012207031</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>412.4599304199219</v>
+        <v>412.4600219726562</v>
       </c>
       <c r="C210" t="n">
         <v>435.489990234375</v>
@@ -6063,7 +6063,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>431.6958923339844</v>
+        <v>431.6959228515625</v>
       </c>
       <c r="C211" t="n">
         <v>455.7999877929688</v>
@@ -6121,7 +6121,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>411.9693908691406</v>
+        <v>411.9694519042969</v>
       </c>
       <c r="C213" t="n">
         <v>433.0899963378906</v>
@@ -6150,7 +6150,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>418.7232360839844</v>
+        <v>418.7232055664062</v>
       </c>
       <c r="C214" t="n">
         <v>440.1900024414062</v>
@@ -6208,7 +6208,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>453.7877197265625</v>
+        <v>453.7877502441406</v>
       </c>
       <c r="C216" t="n">
         <v>475.1600036621094</v>
@@ -6237,7 +6237,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>447.08349609375</v>
+        <v>447.0835266113281</v>
       </c>
       <c r="C217" t="n">
         <v>468.1400146484375</v>
@@ -6266,7 +6266,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>426.6651916503906</v>
+        <v>426.6651306152344</v>
       </c>
       <c r="C218" t="n">
         <v>446.760009765625</v>
@@ -6295,7 +6295,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>442.092529296875</v>
+        <v>442.0925598144531</v>
       </c>
       <c r="C219" t="n">
         <v>461.0199890136719</v>
@@ -6324,7 +6324,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>459.00830078125</v>
+        <v>459.0083312988281</v>
       </c>
       <c r="C220" t="n">
         <v>478.6600036621094</v>
@@ -6382,7 +6382,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>434.1776733398438</v>
+        <v>434.1777038574219</v>
       </c>
       <c r="C222" t="n">
         <v>450.7699890136719</v>
@@ -6411,7 +6411,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>419.9031982421875</v>
+        <v>419.9031677246094</v>
       </c>
       <c r="C223" t="n">
         <v>435.9500122070312</v>
@@ -6440,7 +6440,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>466.4927978515625</v>
+        <v>466.4927673339844</v>
       </c>
       <c r="C224" t="n">
         <v>484.3200073242188</v>
@@ -6469,7 +6469,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>503.9512939453125</v>
+        <v>503.9512634277344</v>
       </c>
       <c r="C225" t="n">
         <v>523.2100219726562</v>
@@ -6498,7 +6498,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>510.6429443359375</v>
+        <v>510.6428833007812</v>
       </c>
       <c r="C226" t="n">
         <v>528.0700073242188</v>
@@ -6556,7 +6556,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>473.4907836914062</v>
+        <v>473.4908142089844</v>
       </c>
       <c r="C228" t="n">
         <v>489.6499938964844</v>
@@ -6585,7 +6585,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>455.7200012207031</v>
+        <v>455.7199401855469</v>
       </c>
       <c r="C229" t="n">
         <v>469.2900085449219</v>
@@ -6614,7 +6614,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>473.1800842285156</v>
+        <v>473.1800537109375</v>
       </c>
       <c r="C230" t="n">
         <v>487.2699890136719</v>
@@ -6730,7 +6730,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>472.8619995117188</v>
+        <v>472.8620300292969</v>
       </c>
       <c r="C234" t="n">
         <v>484.7699890136719</v>
@@ -6788,7 +6788,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>565.1389770507812</v>
+        <v>565.138916015625</v>
       </c>
       <c r="C236" t="n">
         <v>576.6099853515625</v>
@@ -6817,7 +6817,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>578.3017578125</v>
+        <v>578.3018188476562</v>
       </c>
       <c r="C237" t="n">
         <v>590.0399780273438</v>
@@ -6846,7 +6846,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>599.5455322265625</v>
+        <v>599.5454711914062</v>
       </c>
       <c r="C238" t="n">
         <v>609.3200073242188</v>
